--- a/Structure_Data/text.9.14/20260914_19/structure_factor_20260914_19.xlsx
+++ b/Structure_Data/text.9.14/20260914_19/structure_factor_20260914_19.xlsx
@@ -40,7 +40,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:D381"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -248,6 +248,4033 @@
         <v>15.5584880361536</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瓶颈度 beta / Constrictivity (x)</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>0.666666666666667</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瓶颈半径 r_min (um)</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">孔体半径 r_max (um)</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>0.866025403784439</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瓶颈度状态 / Constrictivity Status</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">侵入入口 / Intrusion Inlet</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">low</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">球心邻域 / Center Connectivity</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">算法版本 / Method</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">edt_critical_radii_closed_dilation_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">半径采样 / Radius Sampling</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All positive EDT values</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radius (um)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPSD (total volume fraction)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIP (total volume fraction)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0</v>
+      </c>
+      <c r="B30">
+        <v>0.4085693359375</v>
+      </c>
+      <c r="C30">
+        <v>0.407638549804688</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.5</v>
+      </c>
+      <c r="B31">
+        <v>0.4085693359375</v>
+      </c>
+      <c r="C31">
+        <v>0.407638549804688</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.707106781186548</v>
+      </c>
+      <c r="B32">
+        <v>0.346820831298828</v>
+      </c>
+      <c r="C32">
+        <v>0.315647125244141</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.866025403784439</v>
+      </c>
+      <c r="B33">
+        <v>0.239288330078125</v>
+      </c>
+      <c r="C33">
+        <v>0.174835205078125</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>1</v>
+      </c>
+      <c r="B34">
+        <v>0.201950073242188</v>
+      </c>
+      <c r="C34">
+        <v>0.0338211059570312</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>1.11803398874989</v>
+      </c>
+      <c r="B35">
+        <v>0.182373046875</v>
+      </c>
+      <c r="C35">
+        <v>0.0270614624023438</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>1.22474487139159</v>
+      </c>
+      <c r="B36">
+        <v>0.102157592773438</v>
+      </c>
+      <c r="C36">
+        <v>0.00775146484375</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>1.4142135623731</v>
+      </c>
+      <c r="B37">
+        <v>0.0687255859375</v>
+      </c>
+      <c r="C37">
+        <v>0.00326156616210938</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>1.5</v>
+      </c>
+      <c r="B38">
+        <v>0.0516586303710938</v>
+      </c>
+      <c r="C38">
+        <v>0.00321197509765625</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>1.58113883008419</v>
+      </c>
+      <c r="B39">
+        <v>0.02630615234375</v>
+      </c>
+      <c r="C39">
+        <v>0.00201797485351562</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>1.6583123951777</v>
+      </c>
+      <c r="B40">
+        <v>0.0178108215332031</v>
+      </c>
+      <c r="C40">
+        <v>0.00146484375</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>1.73205080756888</v>
+      </c>
+      <c r="B41">
+        <v>0.0140953063964844</v>
+      </c>
+      <c r="C41">
+        <v>0.00145721435546875</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>1.80277563773199</v>
+      </c>
+      <c r="B42">
+        <v>0.0121116638183594</v>
+      </c>
+      <c r="C42">
+        <v>0.001068115234375</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>1.87082869338697</v>
+      </c>
+      <c r="B43">
+        <v>0.00567245483398438</v>
+      </c>
+      <c r="C43">
+        <v>0.000881195068359375</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>2.06155281280883</v>
+      </c>
+      <c r="B44">
+        <v>0.00115585327148438</v>
+      </c>
+      <c r="C44">
+        <v>0.000690460205078125</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>2.5</v>
+      </c>
+      <c r="B45">
+        <v>0</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46"/>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">弦长分布 / Chord Length</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">periodic_voxel_runs_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore label</t>
+        </is>
+      </c>
+      <c r="B50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voxel size (um)</t>
+        </is>
+      </c>
+      <c r="B51">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodic axes</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sample count</t>
+        </is>
+      </c>
+      <c r="B53">
+        <v>26687</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean (um)</t>
+        </is>
+      </c>
+      <c r="B54">
+        <v>2.00666991419043</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Population std (um)</t>
+        </is>
+      </c>
+      <c r="B55">
+        <v>1.85093710795029</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile method</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inverse_empirical_cdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Axis</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Window-spanning lines</t>
+        </is>
+      </c>
+      <c r="B58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full pore line policy</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one_period_censored</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.05</v>
+      </c>
+      <c r="B61">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.1</v>
+      </c>
+      <c r="B62">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.15</v>
+      </c>
+      <c r="B63">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.2</v>
+      </c>
+      <c r="B64">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.25</v>
+      </c>
+      <c r="B65">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.3</v>
+      </c>
+      <c r="B66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.35</v>
+      </c>
+      <c r="B67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.4</v>
+      </c>
+      <c r="B68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.45</v>
+      </c>
+      <c r="B69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.5</v>
+      </c>
+      <c r="B70">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.55</v>
+      </c>
+      <c r="B71">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.6</v>
+      </c>
+      <c r="B72">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.65</v>
+      </c>
+      <c r="B73">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.7</v>
+      </c>
+      <c r="B74">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.75</v>
+      </c>
+      <c r="B75">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.8</v>
+      </c>
+      <c r="B76">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.85</v>
+      </c>
+      <c r="B77">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.9</v>
+      </c>
+      <c r="B78">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.95</v>
+      </c>
+      <c r="B79">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Count</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Probability mass</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.5</v>
+      </c>
+      <c r="B81">
+        <v>7370</v>
+      </c>
+      <c r="C81">
+        <v>0.276164424626222</v>
+      </c>
+      <c r="D81">
+        <v>0.276164424626222</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>1</v>
+      </c>
+      <c r="B82">
+        <v>4936</v>
+      </c>
+      <c r="C82">
+        <v>0.1849589687863</v>
+      </c>
+      <c r="D82">
+        <v>0.461123393412523</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>1.5</v>
+      </c>
+      <c r="B83">
+        <v>3423</v>
+      </c>
+      <c r="C83">
+        <v>0.128264698167647</v>
+      </c>
+      <c r="D83">
+        <v>0.58938809158017</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>2</v>
+      </c>
+      <c r="B84">
+        <v>2539</v>
+      </c>
+      <c r="C84">
+        <v>0.0951399557837149</v>
+      </c>
+      <c r="D84">
+        <v>0.684528047363885</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>2.5</v>
+      </c>
+      <c r="B85">
+        <v>1970</v>
+      </c>
+      <c r="C85">
+        <v>0.0738187132311612</v>
+      </c>
+      <c r="D85">
+        <v>0.758346760595046</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>3</v>
+      </c>
+      <c r="B86">
+        <v>1544</v>
+      </c>
+      <c r="C86">
+        <v>0.0578558848877731</v>
+      </c>
+      <c r="D86">
+        <v>0.816202645482819</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>3.5</v>
+      </c>
+      <c r="B87">
+        <v>1240</v>
+      </c>
+      <c r="C87">
+        <v>0.0464645707647918</v>
+      </c>
+      <c r="D87">
+        <v>0.862667216247611</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>4</v>
+      </c>
+      <c r="B88">
+        <v>875</v>
+      </c>
+      <c r="C88">
+        <v>0.0327874995316072</v>
+      </c>
+      <c r="D88">
+        <v>0.895454715779218</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>4.5</v>
+      </c>
+      <c r="B89">
+        <v>666</v>
+      </c>
+      <c r="C89">
+        <v>0.0249559710720576</v>
+      </c>
+      <c r="D89">
+        <v>0.920410686851276</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>5</v>
+      </c>
+      <c r="B90">
+        <v>514</v>
+      </c>
+      <c r="C90">
+        <v>0.0192603140105669</v>
+      </c>
+      <c r="D90">
+        <v>0.939671000861843</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>5.5</v>
+      </c>
+      <c r="B91">
+        <v>362</v>
+      </c>
+      <c r="C91">
+        <v>0.0135646569490763</v>
+      </c>
+      <c r="D91">
+        <v>0.953235657810919</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>6</v>
+      </c>
+      <c r="B92">
+        <v>271</v>
+      </c>
+      <c r="C92">
+        <v>0.0101547569977892</v>
+      </c>
+      <c r="D92">
+        <v>0.963390414808708</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>6.5</v>
+      </c>
+      <c r="B93">
+        <v>198</v>
+      </c>
+      <c r="C93">
+        <v>0.00741934275115225</v>
+      </c>
+      <c r="D93">
+        <v>0.970809757559861</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>7</v>
+      </c>
+      <c r="B94">
+        <v>157</v>
+      </c>
+      <c r="C94">
+        <v>0.00588301420167123</v>
+      </c>
+      <c r="D94">
+        <v>0.976692771761532</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>7.5</v>
+      </c>
+      <c r="B95">
+        <v>133</v>
+      </c>
+      <c r="C95">
+        <v>0.00498369992880429</v>
+      </c>
+      <c r="D95">
+        <v>0.981676471690336</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>8</v>
+      </c>
+      <c r="B96">
+        <v>121</v>
+      </c>
+      <c r="C96">
+        <v>0.00453404279237082</v>
+      </c>
+      <c r="D96">
+        <v>0.986210514482707</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>8.5</v>
+      </c>
+      <c r="B97">
+        <v>79</v>
+      </c>
+      <c r="C97">
+        <v>0.00296024281485367</v>
+      </c>
+      <c r="D97">
+        <v>0.989170757297561</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>9</v>
+      </c>
+      <c r="B98">
+        <v>68</v>
+      </c>
+      <c r="C98">
+        <v>0.00254805710645633</v>
+      </c>
+      <c r="D98">
+        <v>0.991718814404017</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>9.5</v>
+      </c>
+      <c r="B99">
+        <v>55</v>
+      </c>
+      <c r="C99">
+        <v>0.00206092854198674</v>
+      </c>
+      <c r="D99">
+        <v>0.993779742946004</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>10</v>
+      </c>
+      <c r="B100">
+        <v>42</v>
+      </c>
+      <c r="C100">
+        <v>0.00157379997751714</v>
+      </c>
+      <c r="D100">
+        <v>0.995353542923521</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>10.5</v>
+      </c>
+      <c r="B101">
+        <v>25</v>
+      </c>
+      <c r="C101">
+        <v>0.000936785700903061</v>
+      </c>
+      <c r="D101">
+        <v>0.996290328624424</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102">
+        <v>11</v>
+      </c>
+      <c r="B102">
+        <v>24</v>
+      </c>
+      <c r="C102">
+        <v>0.000899314272866939</v>
+      </c>
+      <c r="D102">
+        <v>0.997189642897291</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103">
+        <v>11.5</v>
+      </c>
+      <c r="B103">
+        <v>9</v>
+      </c>
+      <c r="C103">
+        <v>0.000337242852325102</v>
+      </c>
+      <c r="D103">
+        <v>0.997526885749616</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104">
+        <v>12</v>
+      </c>
+      <c r="B104">
+        <v>10</v>
+      </c>
+      <c r="C104">
+        <v>0.000374714280361225</v>
+      </c>
+      <c r="D104">
+        <v>0.997901600029977</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105">
+        <v>12.5</v>
+      </c>
+      <c r="B105">
+        <v>8</v>
+      </c>
+      <c r="C105">
+        <v>0.00029977142428898</v>
+      </c>
+      <c r="D105">
+        <v>0.998201371454266</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106">
+        <v>13</v>
+      </c>
+      <c r="B106">
+        <v>11</v>
+      </c>
+      <c r="C106">
+        <v>0.000412185708397347</v>
+      </c>
+      <c r="D106">
+        <v>0.998613557162663</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107">
+        <v>13.5</v>
+      </c>
+      <c r="B107">
+        <v>3</v>
+      </c>
+      <c r="C107">
+        <v>0.000112414284108367</v>
+      </c>
+      <c r="D107">
+        <v>0.998725971446772</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108">
+        <v>14</v>
+      </c>
+      <c r="B108">
+        <v>4</v>
+      </c>
+      <c r="C108">
+        <v>0.00014988571214449</v>
+      </c>
+      <c r="D108">
+        <v>0.998875857158916</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109">
+        <v>14.5</v>
+      </c>
+      <c r="B109">
+        <v>5</v>
+      </c>
+      <c r="C109">
+        <v>0.000187357140180612</v>
+      </c>
+      <c r="D109">
+        <v>0.999063214299097</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110">
+        <v>15</v>
+      </c>
+      <c r="B110">
+        <v>12</v>
+      </c>
+      <c r="C110">
+        <v>0.000449657136433469</v>
+      </c>
+      <c r="D110">
+        <v>0.99951287143553</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111">
+        <v>15.5</v>
+      </c>
+      <c r="B111">
+        <v>2</v>
+      </c>
+      <c r="C111">
+        <v>7.49428560722449e-05</v>
+      </c>
+      <c r="D111">
+        <v>0.999587814291603</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112">
+        <v>16</v>
+      </c>
+      <c r="B112">
+        <v>3</v>
+      </c>
+      <c r="C112">
+        <v>0.000112414284108367</v>
+      </c>
+      <c r="D112">
+        <v>0.999700228575711</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113">
+        <v>16.5</v>
+      </c>
+      <c r="B113">
+        <v>2</v>
+      </c>
+      <c r="C113">
+        <v>7.49428560722449e-05</v>
+      </c>
+      <c r="D113">
+        <v>0.999775171431783</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114">
+        <v>17</v>
+      </c>
+      <c r="B114">
+        <v>2</v>
+      </c>
+      <c r="C114">
+        <v>7.49428560722449e-05</v>
+      </c>
+      <c r="D114">
+        <v>0.999850114287856</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115">
+        <v>17.5</v>
+      </c>
+      <c r="B115">
+        <v>1</v>
+      </c>
+      <c r="C115">
+        <v>3.74714280361225e-05</v>
+      </c>
+      <c r="D115">
+        <v>0.999887585715892</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116">
+        <v>18</v>
+      </c>
+      <c r="B116">
+        <v>2</v>
+      </c>
+      <c r="C116">
+        <v>7.49428560722449e-05</v>
+      </c>
+      <c r="D116">
+        <v>0.999962528571964</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117">
+        <v>18.5</v>
+      </c>
+      <c r="B117">
+        <v>1</v>
+      </c>
+      <c r="C117">
+        <v>3.74714280361225e-05</v>
+      </c>
+      <c r="D117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118"/>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">球接触分布 / Spherical Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">periodic_solid_to_pore_edt_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore label</t>
+        </is>
+      </c>
+      <c r="B122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voxel size (um)</t>
+        </is>
+      </c>
+      <c r="B123">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodic axes</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sample count</t>
+        </is>
+      </c>
+      <c r="B125">
+        <v>155040</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean (um)</t>
+        </is>
+      </c>
+      <c r="B126">
+        <v>0.728816325996384</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Population std (um)</t>
+        </is>
+      </c>
+      <c r="B127">
+        <v>0.417138417122619</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile method</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inverse_empirical_cdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Distance direction</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">solid_to_pore</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Distance convention</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">voxel_center_to_voxel_center</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132">
+        <v>0.05</v>
+      </c>
+      <c r="B132">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133">
+        <v>0.1</v>
+      </c>
+      <c r="B133">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134">
+        <v>0.15</v>
+      </c>
+      <c r="B134">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135">
+        <v>0.2</v>
+      </c>
+      <c r="B135">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136">
+        <v>0.25</v>
+      </c>
+      <c r="B136">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137">
+        <v>0.3</v>
+      </c>
+      <c r="B137">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138">
+        <v>0.35</v>
+      </c>
+      <c r="B138">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139">
+        <v>0.4</v>
+      </c>
+      <c r="B139">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140">
+        <v>0.45</v>
+      </c>
+      <c r="B140">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141">
+        <v>0.5</v>
+      </c>
+      <c r="B141">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142">
+        <v>0.55</v>
+      </c>
+      <c r="B142">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143">
+        <v>0.6</v>
+      </c>
+      <c r="B143">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144">
+        <v>0.65</v>
+      </c>
+      <c r="B144">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145">
+        <v>0.7</v>
+      </c>
+      <c r="B145">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146">
+        <v>0.75</v>
+      </c>
+      <c r="B146">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147">
+        <v>0.8</v>
+      </c>
+      <c r="B147">
+        <v>0.866025403784439</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148">
+        <v>0.85</v>
+      </c>
+      <c r="B148">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149">
+        <v>0.9</v>
+      </c>
+      <c r="B149">
+        <v>1.11803398874989</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150">
+        <v>0.95</v>
+      </c>
+      <c r="B150">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Count</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Probability mass</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152">
+        <v>0.5</v>
+      </c>
+      <c r="B152">
+        <v>81942</v>
+      </c>
+      <c r="C152">
+        <v>0.528521671826625</v>
+      </c>
+      <c r="D152">
+        <v>0.528521671826625</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153">
+        <v>0.707106781186548</v>
+      </c>
+      <c r="B153">
+        <v>38402</v>
+      </c>
+      <c r="C153">
+        <v>0.247690918472652</v>
+      </c>
+      <c r="D153">
+        <v>0.776212590299278</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154">
+        <v>0.866025403784439</v>
+      </c>
+      <c r="B154">
+        <v>10463</v>
+      </c>
+      <c r="C154">
+        <v>0.0674858101135191</v>
+      </c>
+      <c r="D154">
+        <v>0.843698400412797</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155">
+        <v>1</v>
+      </c>
+      <c r="B155">
+        <v>6305</v>
+      </c>
+      <c r="C155">
+        <v>0.0406669246646027</v>
+      </c>
+      <c r="D155">
+        <v>0.884365325077399</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156">
+        <v>1.11803398874989</v>
+      </c>
+      <c r="B156">
+        <v>6078</v>
+      </c>
+      <c r="C156">
+        <v>0.039202786377709</v>
+      </c>
+      <c r="D156">
+        <v>0.923568111455108</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157">
+        <v>1.22474487139159</v>
+      </c>
+      <c r="B157">
+        <v>1913</v>
+      </c>
+      <c r="C157">
+        <v>0.0123387512899897</v>
+      </c>
+      <c r="D157">
+        <v>0.935906862745098</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158">
+        <v>1.4142135623731</v>
+      </c>
+      <c r="B158">
+        <v>798</v>
+      </c>
+      <c r="C158">
+        <v>0.00514705882352941</v>
+      </c>
+      <c r="D158">
+        <v>0.941053921568627</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159">
+        <v>1.5</v>
+      </c>
+      <c r="B159">
+        <v>1578</v>
+      </c>
+      <c r="C159">
+        <v>0.0101780185758514</v>
+      </c>
+      <c r="D159">
+        <v>0.951231940144479</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160">
+        <v>1.58113883008419</v>
+      </c>
+      <c r="B160">
+        <v>856</v>
+      </c>
+      <c r="C160">
+        <v>0.00552115583075335</v>
+      </c>
+      <c r="D160">
+        <v>0.956753095975232</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161">
+        <v>1.6583123951777</v>
+      </c>
+      <c r="B161">
+        <v>578</v>
+      </c>
+      <c r="C161">
+        <v>0.0037280701754386</v>
+      </c>
+      <c r="D161">
+        <v>0.960481166150671</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162">
+        <v>1.73205080756888</v>
+      </c>
+      <c r="B162">
+        <v>172</v>
+      </c>
+      <c r="C162">
+        <v>0.001109391124871</v>
+      </c>
+      <c r="D162">
+        <v>0.961590557275542</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163">
+        <v>1.80277563773199</v>
+      </c>
+      <c r="B163">
+        <v>515</v>
+      </c>
+      <c r="C163">
+        <v>0.00332172342621259</v>
+      </c>
+      <c r="D163">
+        <v>0.964912280701754</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164">
+        <v>1.87082869338697</v>
+      </c>
+      <c r="B164">
+        <v>710</v>
+      </c>
+      <c r="C164">
+        <v>0.00457946336429309</v>
+      </c>
+      <c r="D164">
+        <v>0.969491744066047</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165">
+        <v>2</v>
+      </c>
+      <c r="B165">
+        <v>286</v>
+      </c>
+      <c r="C165">
+        <v>0.00184468524251806</v>
+      </c>
+      <c r="D165">
+        <v>0.971336429308566</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166">
+        <v>2.06155281280883</v>
+      </c>
+      <c r="B166">
+        <v>639</v>
+      </c>
+      <c r="C166">
+        <v>0.00412151702786378</v>
+      </c>
+      <c r="D166">
+        <v>0.975457946336429</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167">
+        <v>2.12132034355964</v>
+      </c>
+      <c r="B167">
+        <v>366</v>
+      </c>
+      <c r="C167">
+        <v>0.00236068111455108</v>
+      </c>
+      <c r="D167">
+        <v>0.97781862745098</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168">
+        <v>2.17944947177034</v>
+      </c>
+      <c r="B168">
+        <v>180</v>
+      </c>
+      <c r="C168">
+        <v>0.0011609907120743</v>
+      </c>
+      <c r="D168">
+        <v>0.978979618163055</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169">
+        <v>2.23606797749979</v>
+      </c>
+      <c r="B169">
+        <v>225</v>
+      </c>
+      <c r="C169">
+        <v>0.00145123839009288</v>
+      </c>
+      <c r="D169">
+        <v>0.980430856553148</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170">
+        <v>2.29128784747792</v>
+      </c>
+      <c r="B170">
+        <v>335</v>
+      </c>
+      <c r="C170">
+        <v>0.00216073271413829</v>
+      </c>
+      <c r="D170">
+        <v>0.982591589267286</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171">
+        <v>2.34520787991171</v>
+      </c>
+      <c r="B171">
+        <v>131</v>
+      </c>
+      <c r="C171">
+        <v>0.000844943240454076</v>
+      </c>
+      <c r="D171">
+        <v>0.98343653250774</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172">
+        <v>2.44948974278318</v>
+      </c>
+      <c r="B172">
+        <v>153</v>
+      </c>
+      <c r="C172">
+        <v>0.000986842105263158</v>
+      </c>
+      <c r="D172">
+        <v>0.984423374613003</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173">
+        <v>2.5</v>
+      </c>
+      <c r="B173">
+        <v>312</v>
+      </c>
+      <c r="C173">
+        <v>0.00201238390092879</v>
+      </c>
+      <c r="D173">
+        <v>0.986435758513932</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174">
+        <v>2.54950975679639</v>
+      </c>
+      <c r="B174">
+        <v>364</v>
+      </c>
+      <c r="C174">
+        <v>0.00234778121775026</v>
+      </c>
+      <c r="D174">
+        <v>0.988783539731682</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175">
+        <v>2.59807621135332</v>
+      </c>
+      <c r="B175">
+        <v>129</v>
+      </c>
+      <c r="C175">
+        <v>0.000832043343653251</v>
+      </c>
+      <c r="D175">
+        <v>0.989615583075335</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176">
+        <v>2.69258240356725</v>
+      </c>
+      <c r="B176">
+        <v>246</v>
+      </c>
+      <c r="C176">
+        <v>0.00158668730650155</v>
+      </c>
+      <c r="D176">
+        <v>0.991202270381837</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177">
+        <v>2.73861278752583</v>
+      </c>
+      <c r="B177">
+        <v>150</v>
+      </c>
+      <c r="C177">
+        <v>0.00096749226006192</v>
+      </c>
+      <c r="D177">
+        <v>0.992169762641899</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178">
+        <v>2.82842712474619</v>
+      </c>
+      <c r="B178">
+        <v>38</v>
+      </c>
+      <c r="C178">
+        <v>0.000245098039215686</v>
+      </c>
+      <c r="D178">
+        <v>0.992414860681115</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179">
+        <v>2.87228132326901</v>
+      </c>
+      <c r="B179">
+        <v>133</v>
+      </c>
+      <c r="C179">
+        <v>0.000857843137254902</v>
+      </c>
+      <c r="D179">
+        <v>0.993272703818369</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180">
+        <v>2.91547594742265</v>
+      </c>
+      <c r="B180">
+        <v>126</v>
+      </c>
+      <c r="C180">
+        <v>0.000812693498452012</v>
+      </c>
+      <c r="D180">
+        <v>0.994085397316821</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181">
+        <v>2.95803989154981</v>
+      </c>
+      <c r="B181">
+        <v>108</v>
+      </c>
+      <c r="C181">
+        <v>0.000696594427244582</v>
+      </c>
+      <c r="D181">
+        <v>0.994781991744066</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182">
+        <v>3</v>
+      </c>
+      <c r="B182">
+        <v>81</v>
+      </c>
+      <c r="C182">
+        <v>0.000522445820433437</v>
+      </c>
+      <c r="D182">
+        <v>0.995304437564499</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183">
+        <v>3.04138126514911</v>
+      </c>
+      <c r="B183">
+        <v>48</v>
+      </c>
+      <c r="C183">
+        <v>0.000309597523219814</v>
+      </c>
+      <c r="D183">
+        <v>0.995614035087719</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184">
+        <v>3.08220700148449</v>
+      </c>
+      <c r="B184">
+        <v>95</v>
+      </c>
+      <c r="C184">
+        <v>0.000612745098039216</v>
+      </c>
+      <c r="D184">
+        <v>0.996226780185758</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185">
+        <v>3.16227766016838</v>
+      </c>
+      <c r="B185">
+        <v>34</v>
+      </c>
+      <c r="C185">
+        <v>0.000219298245614035</v>
+      </c>
+      <c r="D185">
+        <v>0.996446078431373</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186">
+        <v>3.20156211871642</v>
+      </c>
+      <c r="B186">
+        <v>117</v>
+      </c>
+      <c r="C186">
+        <v>0.000754643962848297</v>
+      </c>
+      <c r="D186">
+        <v>0.997200722394221</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187">
+        <v>3.24037034920393</v>
+      </c>
+      <c r="B187">
+        <v>49</v>
+      </c>
+      <c r="C187">
+        <v>0.000316047471620227</v>
+      </c>
+      <c r="D187">
+        <v>0.997516769865841</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188">
+        <v>3.278719262151</v>
+      </c>
+      <c r="B188">
+        <v>19</v>
+      </c>
+      <c r="C188">
+        <v>0.000122549019607843</v>
+      </c>
+      <c r="D188">
+        <v>0.997639318885449</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189">
+        <v>3.3166247903554</v>
+      </c>
+      <c r="B189">
+        <v>21</v>
+      </c>
+      <c r="C189">
+        <v>0.000135448916408669</v>
+      </c>
+      <c r="D189">
+        <v>0.997774767801858</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190">
+        <v>3.35410196624968</v>
+      </c>
+      <c r="B190">
+        <v>57</v>
+      </c>
+      <c r="C190">
+        <v>0.000367647058823529</v>
+      </c>
+      <c r="D190">
+        <v>0.998142414860681</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191">
+        <v>3.39116499156263</v>
+      </c>
+      <c r="B191">
+        <v>27</v>
+      </c>
+      <c r="C191">
+        <v>0.000174148606811146</v>
+      </c>
+      <c r="D191">
+        <v>0.998316563467492</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192">
+        <v>3.46410161513775</v>
+      </c>
+      <c r="B192">
+        <v>3</v>
+      </c>
+      <c r="C192">
+        <v>1.93498452012384e-05</v>
+      </c>
+      <c r="D192">
+        <v>0.998335913312693</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193">
+        <v>3.5</v>
+      </c>
+      <c r="B193">
+        <v>36</v>
+      </c>
+      <c r="C193">
+        <v>0.000232198142414861</v>
+      </c>
+      <c r="D193">
+        <v>0.998568111455108</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194">
+        <v>3.53553390593274</v>
+      </c>
+      <c r="B194">
+        <v>49</v>
+      </c>
+      <c r="C194">
+        <v>0.000316047471620227</v>
+      </c>
+      <c r="D194">
+        <v>0.998884158926729</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195">
+        <v>3.57071421427143</v>
+      </c>
+      <c r="B195">
+        <v>21</v>
+      </c>
+      <c r="C195">
+        <v>0.000135448916408669</v>
+      </c>
+      <c r="D195">
+        <v>0.999019607843137</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196">
+        <v>3.60555127546399</v>
+      </c>
+      <c r="B196">
+        <v>10</v>
+      </c>
+      <c r="C196">
+        <v>6.4499484004128e-05</v>
+      </c>
+      <c r="D196">
+        <v>0.999084107327141</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197">
+        <v>3.64005494464026</v>
+      </c>
+      <c r="B197">
+        <v>27</v>
+      </c>
+      <c r="C197">
+        <v>0.000174148606811146</v>
+      </c>
+      <c r="D197">
+        <v>0.999258255933953</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198">
+        <v>3.67423461417477</v>
+      </c>
+      <c r="B198">
+        <v>24</v>
+      </c>
+      <c r="C198">
+        <v>0.000154798761609907</v>
+      </c>
+      <c r="D198">
+        <v>0.999413054695562</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199">
+        <v>3.74165738677394</v>
+      </c>
+      <c r="B199">
+        <v>13</v>
+      </c>
+      <c r="C199">
+        <v>8.38493292053664e-05</v>
+      </c>
+      <c r="D199">
+        <v>0.999496904024768</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200">
+        <v>3.77491721763537</v>
+      </c>
+      <c r="B200">
+        <v>9</v>
+      </c>
+      <c r="C200">
+        <v>5.80495356037152e-05</v>
+      </c>
+      <c r="D200">
+        <v>0.999554953560371</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201">
+        <v>3.80788655293195</v>
+      </c>
+      <c r="B201">
+        <v>5</v>
+      </c>
+      <c r="C201">
+        <v>3.2249742002064e-05</v>
+      </c>
+      <c r="D201">
+        <v>0.999587203302374</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202">
+        <v>3.8405728739343</v>
+      </c>
+      <c r="B202">
+        <v>10</v>
+      </c>
+      <c r="C202">
+        <v>6.4499484004128e-05</v>
+      </c>
+      <c r="D202">
+        <v>0.999651702786378</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203">
+        <v>3.90512483795333</v>
+      </c>
+      <c r="B203">
+        <v>16</v>
+      </c>
+      <c r="C203">
+        <v>0.000103199174406605</v>
+      </c>
+      <c r="D203">
+        <v>0.999754901960784</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204">
+        <v>3.93700393700591</v>
+      </c>
+      <c r="B204">
+        <v>13</v>
+      </c>
+      <c r="C204">
+        <v>8.38493292053664e-05</v>
+      </c>
+      <c r="D204">
+        <v>0.99983875128999</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205">
+        <v>4.03112887414927</v>
+      </c>
+      <c r="B205">
+        <v>9</v>
+      </c>
+      <c r="C205">
+        <v>5.80495356037152e-05</v>
+      </c>
+      <c r="D205">
+        <v>0.999896800825593</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206">
+        <v>4.06201920231798</v>
+      </c>
+      <c r="B206">
+        <v>8</v>
+      </c>
+      <c r="C206">
+        <v>5.15995872033024e-05</v>
+      </c>
+      <c r="D206">
+        <v>0.999948400412797</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207">
+        <v>4.09267638593623</v>
+      </c>
+      <c r="B207">
+        <v>1</v>
+      </c>
+      <c r="C207">
+        <v>6.4499484004128e-06</v>
+      </c>
+      <c r="D207">
+        <v>0.999954850361197</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208">
+        <v>4.12310562561766</v>
+      </c>
+      <c r="B208">
+        <v>2</v>
+      </c>
+      <c r="C208">
+        <v>1.28998968008256e-05</v>
+      </c>
+      <c r="D208">
+        <v>0.999967750257998</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209">
+        <v>4.15331193145904</v>
+      </c>
+      <c r="B209">
+        <v>3</v>
+      </c>
+      <c r="C209">
+        <v>1.93498452012384e-05</v>
+      </c>
+      <c r="D209">
+        <v>0.999987100103199</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210">
+        <v>4.18330013267038</v>
+      </c>
+      <c r="B210">
+        <v>1</v>
+      </c>
+      <c r="C210">
+        <v>6.4499484004128e-06</v>
+      </c>
+      <c r="D210">
+        <v>0.9999935500516</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211">
+        <v>4.30116263352131</v>
+      </c>
+      <c r="B211">
+        <v>1</v>
+      </c>
+      <c r="C211">
+        <v>6.4499484004128e-06</v>
+      </c>
+      <c r="D211">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212"/>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">两点相关函数 / Two-Point Correlation</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">periodic_fft_radial_shells_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore label</t>
+        </is>
+      </c>
+      <c r="B216">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Porosity</t>
+        </is>
+      </c>
+      <c r="B217">
+        <v>0.4085693359375</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voxel size (um)</t>
+        </is>
+      </c>
+      <c r="B218">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodic axes</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radial bins</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bin_0_origin_only; bin_k: (k-1)*h &lt; distance &lt;= k*h</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Normalization</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">joint_probability; C(0)=porosity</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radius upper edge (um)</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Displacement count</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean distance (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223">
+        <v>0</v>
+      </c>
+      <c r="B223">
+        <v>0.4085693359375</v>
+      </c>
+      <c r="C223">
+        <v>1</v>
+      </c>
+      <c r="D223">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224">
+        <v>0.5</v>
+      </c>
+      <c r="B224">
+        <v>0.3096923828125</v>
+      </c>
+      <c r="C224">
+        <v>6</v>
+      </c>
+      <c r="D224">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225">
+        <v>1</v>
+      </c>
+      <c r="B225">
+        <v>0.265816908616286</v>
+      </c>
+      <c r="C225">
+        <v>26</v>
+      </c>
+      <c r="D225">
+        <v>0.82359556171208</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226">
+        <v>1.5</v>
+      </c>
+      <c r="B226">
+        <v>0.220950995551215</v>
+      </c>
+      <c r="C226">
+        <v>90</v>
+      </c>
+      <c r="D226">
+        <v>1.31330283768748</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227">
+        <v>2</v>
+      </c>
+      <c r="B227">
+        <v>0.199015944751341</v>
+      </c>
+      <c r="C227">
+        <v>134</v>
+      </c>
+      <c r="D227">
+        <v>1.76619125712671</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228">
+        <v>2.5</v>
+      </c>
+      <c r="B228">
+        <v>0.189567388490189</v>
+      </c>
+      <c r="C228">
+        <v>258</v>
+      </c>
+      <c r="D228">
+        <v>2.25329087515144</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229">
+        <v>3</v>
+      </c>
+      <c r="B229">
+        <v>0.185285782232517</v>
+      </c>
+      <c r="C229">
+        <v>410</v>
+      </c>
+      <c r="D229">
+        <v>2.77015092047628</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230">
+        <v>3.5</v>
+      </c>
+      <c r="B230">
+        <v>0.183359648052015</v>
+      </c>
+      <c r="C230">
+        <v>494</v>
+      </c>
+      <c r="D230">
+        <v>3.26511495914839</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231">
+        <v>4</v>
+      </c>
+      <c r="B231">
+        <v>0.182189300094826</v>
+      </c>
+      <c r="C231">
+        <v>690</v>
+      </c>
+      <c r="D231">
+        <v>3.74137726298534</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232">
+        <v>4.5</v>
+      </c>
+      <c r="B232">
+        <v>0.180857557268995</v>
+      </c>
+      <c r="C232">
+        <v>962</v>
+      </c>
+      <c r="D232">
+        <v>4.25479734207796</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233">
+        <v>5</v>
+      </c>
+      <c r="B233">
+        <v>0.179663847487264</v>
+      </c>
+      <c r="C233">
+        <v>1098</v>
+      </c>
+      <c r="D233">
+        <v>4.75998893674797</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234">
+        <v>5.5</v>
+      </c>
+      <c r="B234">
+        <v>0.17850235549688</v>
+      </c>
+      <c r="C234">
+        <v>1406</v>
+      </c>
+      <c r="D234">
+        <v>5.25297061080461</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235">
+        <v>6</v>
+      </c>
+      <c r="B235">
+        <v>0.177241771393402</v>
+      </c>
+      <c r="C235">
+        <v>1578</v>
+      </c>
+      <c r="D235">
+        <v>5.7433060626392</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236">
+        <v>6.5</v>
+      </c>
+      <c r="B236">
+        <v>0.176068701994549</v>
+      </c>
+      <c r="C236">
+        <v>2018</v>
+      </c>
+      <c r="D236">
+        <v>6.24308779578354</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237">
+        <v>7</v>
+      </c>
+      <c r="B237">
+        <v>0.174847590628086</v>
+      </c>
+      <c r="C237">
+        <v>2342</v>
+      </c>
+      <c r="D237">
+        <v>6.75452277955052</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238">
+        <v>7.5</v>
+      </c>
+      <c r="B238">
+        <v>0.173942038754034</v>
+      </c>
+      <c r="C238">
+        <v>2634</v>
+      </c>
+      <c r="D238">
+        <v>7.25880828593797</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239">
+        <v>8</v>
+      </c>
+      <c r="B239">
+        <v>0.173257112991281</v>
+      </c>
+      <c r="C239">
+        <v>2930</v>
+      </c>
+      <c r="D239">
+        <v>7.7481595567505</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240">
+        <v>8.5</v>
+      </c>
+      <c r="B240">
+        <v>0.172639560867659</v>
+      </c>
+      <c r="C240">
+        <v>3402</v>
+      </c>
+      <c r="D240">
+        <v>8.24275983872338</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241">
+        <v>9</v>
+      </c>
+      <c r="B241">
+        <v>0.17203832267804</v>
+      </c>
+      <c r="C241">
+        <v>3926</v>
+      </c>
+      <c r="D241">
+        <v>8.74722614715433</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242">
+        <v>9.5</v>
+      </c>
+      <c r="B242">
+        <v>0.171456014612612</v>
+      </c>
+      <c r="C242">
+        <v>4266</v>
+      </c>
+      <c r="D242">
+        <v>9.24875254641385</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243">
+        <v>10</v>
+      </c>
+      <c r="B243">
+        <v>0.170879236588266</v>
+      </c>
+      <c r="C243">
+        <v>4730</v>
+      </c>
+      <c r="D243">
+        <v>9.74564847205822</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244">
+        <v>10.5</v>
+      </c>
+      <c r="B244">
+        <v>0.170224879657725</v>
+      </c>
+      <c r="C244">
+        <v>5510</v>
+      </c>
+      <c r="D244">
+        <v>10.2542063522575</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245">
+        <v>11</v>
+      </c>
+      <c r="B245">
+        <v>0.169570973604457</v>
+      </c>
+      <c r="C245">
+        <v>5562</v>
+      </c>
+      <c r="D245">
+        <v>10.7542478228895</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246">
+        <v>11.5</v>
+      </c>
+      <c r="B246">
+        <v>0.16887928074496</v>
+      </c>
+      <c r="C246">
+        <v>6410</v>
+      </c>
+      <c r="D246">
+        <v>11.244987895373</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247">
+        <v>12</v>
+      </c>
+      <c r="B247">
+        <v>0.168227457744265</v>
+      </c>
+      <c r="C247">
+        <v>6894</v>
+      </c>
+      <c r="D247">
+        <v>11.7450714339387</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248">
+        <v>12.5</v>
+      </c>
+      <c r="B248">
+        <v>0.167742476826198</v>
+      </c>
+      <c r="C248">
+        <v>7490</v>
+      </c>
+      <c r="D248">
+        <v>12.2441426243554</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249">
+        <v>13</v>
+      </c>
+      <c r="B249">
+        <v>0.167297548980972</v>
+      </c>
+      <c r="C249">
+        <v>8258</v>
+      </c>
+      <c r="D249">
+        <v>12.7444225452559</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250">
+        <v>13.5</v>
+      </c>
+      <c r="B250">
+        <v>0.166920811859056</v>
+      </c>
+      <c r="C250">
+        <v>8994</v>
+      </c>
+      <c r="D250">
+        <v>13.2528519154988</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251">
+        <v>14</v>
+      </c>
+      <c r="B251">
+        <v>0.166585608455505</v>
+      </c>
+      <c r="C251">
+        <v>9446</v>
+      </c>
+      <c r="D251">
+        <v>13.7542803671108</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252">
+        <v>14.5</v>
+      </c>
+      <c r="B252">
+        <v>0.166275223215684</v>
+      </c>
+      <c r="C252">
+        <v>9978</v>
+      </c>
+      <c r="D252">
+        <v>14.2483018118451</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253">
+        <v>15</v>
+      </c>
+      <c r="B253">
+        <v>0.166017194307135</v>
+      </c>
+      <c r="C253">
+        <v>11138</v>
+      </c>
+      <c r="D253">
+        <v>14.7478143756516</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254">
+        <v>15.5</v>
+      </c>
+      <c r="B254">
+        <v>0.165762304486297</v>
+      </c>
+      <c r="C254">
+        <v>11406</v>
+      </c>
+      <c r="D254">
+        <v>15.2452282287867</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255">
+        <v>16</v>
+      </c>
+      <c r="B255">
+        <v>0.165516327693022</v>
+      </c>
+      <c r="C255">
+        <v>12575</v>
+      </c>
+      <c r="D255">
+        <v>15.7433814113418</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256">
+        <v>16.5</v>
+      </c>
+      <c r="B256">
+        <v>0.165277963260636</v>
+      </c>
+      <c r="C256">
+        <v>12848</v>
+      </c>
+      <c r="D256">
+        <v>16.2480191911098</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257">
+        <v>17</v>
+      </c>
+      <c r="B257">
+        <v>0.165065470580043</v>
+      </c>
+      <c r="C257">
+        <v>12060</v>
+      </c>
+      <c r="D257">
+        <v>16.7498118527173</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258">
+        <v>17.5</v>
+      </c>
+      <c r="B258">
+        <v>0.16497797434389</v>
+      </c>
+      <c r="C258">
+        <v>11804</v>
+      </c>
+      <c r="D258">
+        <v>17.2477889982035</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259">
+        <v>18</v>
+      </c>
+      <c r="B259">
+        <v>0.164900569874217</v>
+      </c>
+      <c r="C259">
+        <v>11016</v>
+      </c>
+      <c r="D259">
+        <v>17.7466461218484</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260">
+        <v>18.5</v>
+      </c>
+      <c r="B260">
+        <v>0.164829107979748</v>
+      </c>
+      <c r="C260">
+        <v>10700</v>
+      </c>
+      <c r="D260">
+        <v>18.2476461964778</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261">
+        <v>19</v>
+      </c>
+      <c r="B261">
+        <v>0.164750133200032</v>
+      </c>
+      <c r="C261">
+        <v>9756</v>
+      </c>
+      <c r="D261">
+        <v>18.7461608461768</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262">
+        <v>19.5</v>
+      </c>
+      <c r="B262">
+        <v>0.16465513621427</v>
+      </c>
+      <c r="C262">
+        <v>9224</v>
+      </c>
+      <c r="D262">
+        <v>19.2443623593903</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263">
+        <v>20</v>
+      </c>
+      <c r="B263">
+        <v>0.164569582517208</v>
+      </c>
+      <c r="C263">
+        <v>8408</v>
+      </c>
+      <c r="D263">
+        <v>19.7427539394596</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264">
+        <v>20.5</v>
+      </c>
+      <c r="B264">
+        <v>0.164475589942625</v>
+      </c>
+      <c r="C264">
+        <v>7452</v>
+      </c>
+      <c r="D264">
+        <v>20.2349524648069</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265">
+        <v>21</v>
+      </c>
+      <c r="B265">
+        <v>0.164508434859189</v>
+      </c>
+      <c r="C265">
+        <v>7040</v>
+      </c>
+      <c r="D265">
+        <v>20.7366941177926</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266">
+        <v>21.5</v>
+      </c>
+      <c r="B266">
+        <v>0.164450800787542</v>
+      </c>
+      <c r="C266">
+        <v>5820</v>
+      </c>
+      <c r="D266">
+        <v>21.2419860619221</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267">
+        <v>22</v>
+      </c>
+      <c r="B267">
+        <v>0.164549752532459</v>
+      </c>
+      <c r="C267">
+        <v>4880</v>
+      </c>
+      <c r="D267">
+        <v>21.7372039907627</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268">
+        <v>22.5</v>
+      </c>
+      <c r="B268">
+        <v>0.164518809900051</v>
+      </c>
+      <c r="C268">
+        <v>3936</v>
+      </c>
+      <c r="D268">
+        <v>22.2302479362391</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269">
+        <v>23</v>
+      </c>
+      <c r="B269">
+        <v>0.164490901060445</v>
+      </c>
+      <c r="C269">
+        <v>2999</v>
+      </c>
+      <c r="D269">
+        <v>22.7334385317465</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270">
+        <v>23.5</v>
+      </c>
+      <c r="B270">
+        <v>0.164477903033615</v>
+      </c>
+      <c r="C270">
+        <v>2180</v>
+      </c>
+      <c r="D270">
+        <v>23.2369587045059</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271">
+        <v>24</v>
+      </c>
+      <c r="B271">
+        <v>0.164482710096571</v>
+      </c>
+      <c r="C271">
+        <v>1620</v>
+      </c>
+      <c r="D271">
+        <v>23.7279225769148</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272">
+        <v>24.5</v>
+      </c>
+      <c r="B272">
+        <v>0.164473760996433</v>
+      </c>
+      <c r="C272">
+        <v>1208</v>
+      </c>
+      <c r="D272">
+        <v>24.2151258882127</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273">
+        <v>25</v>
+      </c>
+      <c r="B273">
+        <v>0.164563780377625</v>
+      </c>
+      <c r="C273">
+        <v>942</v>
+      </c>
+      <c r="D273">
+        <v>24.7383759194601</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274">
+        <v>25.5</v>
+      </c>
+      <c r="B274">
+        <v>0.164739478124331</v>
+      </c>
+      <c r="C274">
+        <v>584</v>
+      </c>
+      <c r="D274">
+        <v>25.2823739766508</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275">
+        <v>26</v>
+      </c>
+      <c r="B275">
+        <v>0.164917395148479</v>
+      </c>
+      <c r="C275">
+        <v>284</v>
+      </c>
+      <c r="D275">
+        <v>25.7666230311241</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276">
+        <v>26.5</v>
+      </c>
+      <c r="B276">
+        <v>0.164976755777995</v>
+      </c>
+      <c r="C276">
+        <v>192</v>
+      </c>
+      <c r="D276">
+        <v>26.1687296580041</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277">
+        <v>27</v>
+      </c>
+      <c r="B277">
+        <v>0.165483988248385</v>
+      </c>
+      <c r="C277">
+        <v>104</v>
+      </c>
+      <c r="D277">
+        <v>26.6774814912972</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278">
+        <v>27.5</v>
+      </c>
+      <c r="B278">
+        <v>0.165769577026367</v>
+      </c>
+      <c r="C278">
+        <v>24</v>
+      </c>
+      <c r="D278">
+        <v>27.2129968013123</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279">
+        <v>28</v>
+      </c>
+      <c r="B279">
+        <v>0.165504455566406</v>
+      </c>
+      <c r="C279">
+        <v>1</v>
+      </c>
+      <c r="D279">
+        <v>27.712812921102</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x displacement (um)</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281">
+        <v>0</v>
+      </c>
+      <c r="B281">
+        <v>0.4085693359375</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282">
+        <v>0.5</v>
+      </c>
+      <c r="B282">
+        <v>0.306766510009766</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283">
+        <v>1</v>
+      </c>
+      <c r="B283">
+        <v>0.24200439453125</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284">
+        <v>1.5</v>
+      </c>
+      <c r="B284">
+        <v>0.206039428710938</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285">
+        <v>2</v>
+      </c>
+      <c r="B285">
+        <v>0.192153930664062</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286">
+        <v>2.5</v>
+      </c>
+      <c r="B286">
+        <v>0.185661315917969</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287">
+        <v>3</v>
+      </c>
+      <c r="B287">
+        <v>0.182415008544922</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288">
+        <v>3.5</v>
+      </c>
+      <c r="B288">
+        <v>0.180335998535156</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289">
+        <v>4</v>
+      </c>
+      <c r="B289">
+        <v>0.179187774658203</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290">
+        <v>4.5</v>
+      </c>
+      <c r="B290">
+        <v>0.178817749023438</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291">
+        <v>5</v>
+      </c>
+      <c r="B291">
+        <v>0.177810668945312</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292">
+        <v>5.5</v>
+      </c>
+      <c r="B292">
+        <v>0.177120208740234</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293">
+        <v>6</v>
+      </c>
+      <c r="B293">
+        <v>0.176509857177734</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294">
+        <v>6.5</v>
+      </c>
+      <c r="B294">
+        <v>0.174545288085938</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295">
+        <v>7</v>
+      </c>
+      <c r="B295">
+        <v>0.172153472900391</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296">
+        <v>7.5</v>
+      </c>
+      <c r="B296">
+        <v>0.169868469238281</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297">
+        <v>8</v>
+      </c>
+      <c r="B297">
+        <v>0.169261932373047</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298">
+        <v>8.5</v>
+      </c>
+      <c r="B298">
+        <v>0.16888427734375</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299">
+        <v>9</v>
+      </c>
+      <c r="B299">
+        <v>0.16790771484375</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300">
+        <v>9.5</v>
+      </c>
+      <c r="B300">
+        <v>0.167217254638672</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301">
+        <v>10</v>
+      </c>
+      <c r="B301">
+        <v>0.167186737060547</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302">
+        <v>10.5</v>
+      </c>
+      <c r="B302">
+        <v>0.167106628417969</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303">
+        <v>11</v>
+      </c>
+      <c r="B303">
+        <v>0.167194366455078</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304">
+        <v>11.5</v>
+      </c>
+      <c r="B304">
+        <v>0.167579650878906</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305">
+        <v>12</v>
+      </c>
+      <c r="B305">
+        <v>0.16790771484375</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306">
+        <v>12.5</v>
+      </c>
+      <c r="B306">
+        <v>0.167121887207031</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307">
+        <v>13</v>
+      </c>
+      <c r="B307">
+        <v>0.166202545166016</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308">
+        <v>13.5</v>
+      </c>
+      <c r="B308">
+        <v>0.165153503417969</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309">
+        <v>14</v>
+      </c>
+      <c r="B309">
+        <v>0.164878845214844</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310">
+        <v>14.5</v>
+      </c>
+      <c r="B310">
+        <v>0.164752960205078</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311">
+        <v>15</v>
+      </c>
+      <c r="B311">
+        <v>0.164752960205078</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312">
+        <v>15.5</v>
+      </c>
+      <c r="B312">
+        <v>0.165843963623047</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313">
+        <v>16</v>
+      </c>
+      <c r="B313">
+        <v>0.166244506835938</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t xml:space="preserve">y displacement (um)</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315">
+        <v>0</v>
+      </c>
+      <c r="B315">
+        <v>0.4085693359375</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316">
+        <v>0.5</v>
+      </c>
+      <c r="B316">
+        <v>0.307033538818359</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317">
+        <v>1</v>
+      </c>
+      <c r="B317">
+        <v>0.24102783203125</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318">
+        <v>1.5</v>
+      </c>
+      <c r="B318">
+        <v>0.204097747802734</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319">
+        <v>2</v>
+      </c>
+      <c r="B319">
+        <v>0.190471649169922</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320">
+        <v>2.5</v>
+      </c>
+      <c r="B320">
+        <v>0.185649871826172</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321">
+        <v>3</v>
+      </c>
+      <c r="B321">
+        <v>0.184593200683594</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322">
+        <v>3.5</v>
+      </c>
+      <c r="B322">
+        <v>0.183643341064453</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323">
+        <v>4</v>
+      </c>
+      <c r="B323">
+        <v>0.182853698730469</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324">
+        <v>4.5</v>
+      </c>
+      <c r="B324">
+        <v>0.181709289550781</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325">
+        <v>5</v>
+      </c>
+      <c r="B325">
+        <v>0.180366516113281</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326">
+        <v>5.5</v>
+      </c>
+      <c r="B326">
+        <v>0.178359985351562</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327">
+        <v>6</v>
+      </c>
+      <c r="B327">
+        <v>0.176094055175781</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328">
+        <v>6.5</v>
+      </c>
+      <c r="B328">
+        <v>0.175056457519531</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329">
+        <v>7</v>
+      </c>
+      <c r="B329">
+        <v>0.174247741699219</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330">
+        <v>7.5</v>
+      </c>
+      <c r="B330">
+        <v>0.173923492431641</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331">
+        <v>8</v>
+      </c>
+      <c r="B331">
+        <v>0.174121856689453</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332">
+        <v>8.5</v>
+      </c>
+      <c r="B332">
+        <v>0.174304962158203</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333">
+        <v>9</v>
+      </c>
+      <c r="B333">
+        <v>0.174629211425781</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334">
+        <v>9.5</v>
+      </c>
+      <c r="B334">
+        <v>0.174129486083984</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335">
+        <v>10</v>
+      </c>
+      <c r="B335">
+        <v>0.172611236572266</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336">
+        <v>10.5</v>
+      </c>
+      <c r="B336">
+        <v>0.170719146728516</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337">
+        <v>11</v>
+      </c>
+      <c r="B337">
+        <v>0.168830871582031</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338">
+        <v>11.5</v>
+      </c>
+      <c r="B338">
+        <v>0.167133331298828</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339">
+        <v>12</v>
+      </c>
+      <c r="B339">
+        <v>0.165786743164062</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340">
+        <v>12.5</v>
+      </c>
+      <c r="B340">
+        <v>0.165306091308594</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341">
+        <v>13</v>
+      </c>
+      <c r="B341">
+        <v>0.165977478027344</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342">
+        <v>13.5</v>
+      </c>
+      <c r="B342">
+        <v>0.166828155517578</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343">
+        <v>14</v>
+      </c>
+      <c r="B343">
+        <v>0.167255401611328</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344">
+        <v>14.5</v>
+      </c>
+      <c r="B344">
+        <v>0.166332244873047</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345">
+        <v>15</v>
+      </c>
+      <c r="B345">
+        <v>0.165569305419922</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346">
+        <v>15.5</v>
+      </c>
+      <c r="B346">
+        <v>0.164947509765625</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347">
+        <v>16</v>
+      </c>
+      <c r="B347">
+        <v>0.164901733398438</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">z displacement (um)</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349">
+        <v>0</v>
+      </c>
+      <c r="B349">
+        <v>0.4085693359375</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350">
+        <v>0.5</v>
+      </c>
+      <c r="B350">
+        <v>0.315277099609375</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351">
+        <v>1</v>
+      </c>
+      <c r="B351">
+        <v>0.253116607666016</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352">
+        <v>1.5</v>
+      </c>
+      <c r="B352">
+        <v>0.214920043945312</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353">
+        <v>2</v>
+      </c>
+      <c r="B353">
+        <v>0.197231292724609</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354">
+        <v>2.5</v>
+      </c>
+      <c r="B354">
+        <v>0.188976287841797</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355">
+        <v>3</v>
+      </c>
+      <c r="B355">
+        <v>0.186538696289062</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356">
+        <v>3.5</v>
+      </c>
+      <c r="B356">
+        <v>0.185466766357422</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357">
+        <v>4</v>
+      </c>
+      <c r="B357">
+        <v>0.1851806640625</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358">
+        <v>4.5</v>
+      </c>
+      <c r="B358">
+        <v>0.183509826660156</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359">
+        <v>5</v>
+      </c>
+      <c r="B359">
+        <v>0.182182312011719</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360">
+        <v>5.5</v>
+      </c>
+      <c r="B360">
+        <v>0.181262969970703</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361">
+        <v>6</v>
+      </c>
+      <c r="B361">
+        <v>0.180152893066406</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362">
+        <v>6.5</v>
+      </c>
+      <c r="B362">
+        <v>0.179084777832031</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363">
+        <v>7</v>
+      </c>
+      <c r="B363">
+        <v>0.178478240966797</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364">
+        <v>7.5</v>
+      </c>
+      <c r="B364">
+        <v>0.177600860595703</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365">
+        <v>8</v>
+      </c>
+      <c r="B365">
+        <v>0.176856994628906</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366">
+        <v>8.5</v>
+      </c>
+      <c r="B366">
+        <v>0.175266265869141</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367">
+        <v>9</v>
+      </c>
+      <c r="B367">
+        <v>0.173797607421875</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368">
+        <v>9.5</v>
+      </c>
+      <c r="B368">
+        <v>0.173328399658203</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369">
+        <v>10</v>
+      </c>
+      <c r="B369">
+        <v>0.173053741455078</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370">
+        <v>10.5</v>
+      </c>
+      <c r="B370">
+        <v>0.172470092773438</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371">
+        <v>11</v>
+      </c>
+      <c r="B371">
+        <v>0.1715087890625</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372">
+        <v>11.5</v>
+      </c>
+      <c r="B372">
+        <v>0.171138763427734</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373">
+        <v>12</v>
+      </c>
+      <c r="B373">
+        <v>0.171504974365234</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374">
+        <v>12.5</v>
+      </c>
+      <c r="B374">
+        <v>0.172603607177734</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375">
+        <v>13</v>
+      </c>
+      <c r="B375">
+        <v>0.17413330078125</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376">
+        <v>13.5</v>
+      </c>
+      <c r="B376">
+        <v>0.175048828125</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377">
+        <v>14</v>
+      </c>
+      <c r="B377">
+        <v>0.174644470214844</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378">
+        <v>14.5</v>
+      </c>
+      <c r="B378">
+        <v>0.173103332519531</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379">
+        <v>15</v>
+      </c>
+      <c r="B379">
+        <v>0.172157287597656</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380">
+        <v>15.5</v>
+      </c>
+      <c r="B380">
+        <v>0.171943664550781</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381">
+        <v>16</v>
+      </c>
+      <c r="B381">
+        <v>0.172142028808594</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>